--- a/tools/importer/reports/import-symptom-page.report.xlsx
+++ b/tools/importer/reports/import-symptom-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>symptom-page</t>
   </si>
   <si>
-    <t>2026-08-24T04:38:54.600Z</t>
+    <t>2026-08-25T02:08:08.144Z</t>
   </si>
   <si>
     <t>Abdominal pain in children - causes and when to see a doctor | healthdirect</t>
@@ -70,7 +70,7 @@
     <t>abdominal-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:38:46.858Z</t>
+    <t>2026-08-25T02:08:01.643Z</t>
   </si>
   <si>
     <t>Abdominal pain - causes, self-care and treatments | healthdirect</t>
@@ -88,7 +88,7 @@
     <t>aches-and-pains</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:04.069Z</t>
+    <t>2026-08-25T02:08:18.182Z</t>
   </si>
   <si>
     <t>Aches and pains | healthdirect</t>
@@ -106,7 +106,7 @@
     <t>addiction-withdrawal</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:10.494Z</t>
+    <t>2026-08-25T02:08:25.300Z</t>
   </si>
   <si>
     <t>Addiction withdrawal | healthdirect</t>
@@ -124,7 +124,7 @@
     <t>adrenal-fatigue</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:18.468Z</t>
+    <t>2026-08-25T02:08:32.473Z</t>
   </si>
   <si>
     <t>Adrenal fatigue - symptoms and treatment | healthdirect</t>
@@ -139,7 +139,7 @@
     <t>anal-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:26.941Z</t>
+    <t>2026-08-25T02:08:39.970Z</t>
   </si>
   <si>
     <t>Anal pain - rectal pain, fissures, symptoms and treatments | healthdirect</t>
@@ -154,7 +154,7 @@
     <t>anosmia-loss-of-smell</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:33.871Z</t>
+    <t>2026-08-25T02:08:47.939Z</t>
   </si>
   <si>
     <t>Anosmia (loss of smell) | healthdirect</t>
@@ -172,7 +172,7 @@
     <t>anxiety-in-teenagers</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:43.242Z</t>
+    <t>2026-08-25T02:09:02.505Z</t>
   </si>
   <si>
     <t>Anxiety in teenagers - symptoms, treatment and support | healthdirect</t>
@@ -190,7 +190,7 @@
     <t>anxiety</t>
   </si>
   <si>
-    <t>2026-08-24T04:18:07.637Z</t>
+    <t>2026-08-25T02:08:55.754Z</t>
   </si>
   <si>
     <t>Anxiety | healthdirect</t>
@@ -205,7 +205,7 @@
     <t>black-eye</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:51.947Z</t>
+    <t>2026-08-25T02:09:10.784Z</t>
   </si>
   <si>
     <t>Black eye (periorbital haematoma) - treatment and causes | healthdirect</t>
@@ -220,7 +220,7 @@
     <t>blackouts</t>
   </si>
   <si>
-    <t>2026-08-24T04:39:59.739Z</t>
+    <t>2026-08-25T02:09:18.366Z</t>
   </si>
   <si>
     <t>Blackouts | healthdirect</t>
@@ -235,7 +235,7 @@
     <t>bleeding-between-periods</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:07.680Z</t>
+    <t>2026-08-25T02:09:24.771Z</t>
   </si>
   <si>
     <t>Bleeding between periods | healthdirect</t>
@@ -250,7 +250,7 @@
     <t>bleeding-gums-and-dental-bleeding</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:15.922Z</t>
+    <t>2026-08-25T02:09:32.728Z</t>
   </si>
   <si>
     <t>Bleeding gums and dental bleeding | healthdirect</t>
@@ -268,7 +268,7 @@
     <t>bloating</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:23.869Z</t>
+    <t>2026-08-25T02:09:41.739Z</t>
   </si>
   <si>
     <t>Bloating - causes, treatment and prevention | healthdirect</t>
@@ -283,7 +283,7 @@
     <t>blocked-nose</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:30.547Z</t>
+    <t>2026-08-25T02:09:48.443Z</t>
   </si>
   <si>
     <t>Blocked nose - nasal congestion, treatment | healthdirect</t>
@@ -298,7 +298,7 @@
     <t>blood-in-semen</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:38.204Z</t>
+    <t>2026-08-25T02:09:55.084Z</t>
   </si>
   <si>
     <t>Blood in semen (haematospermia): causes and treatment | healthdirect</t>
@@ -313,7 +313,7 @@
     <t>blood-in-stool</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:46.990Z</t>
+    <t>2026-08-25T02:10:02.581Z</t>
   </si>
   <si>
     <t>Blood in stool | healthdirect</t>
@@ -328,7 +328,7 @@
     <t>blood-in-urine</t>
   </si>
   <si>
-    <t>2026-08-24T04:40:55.040Z</t>
+    <t>2026-08-25T02:10:09.169Z</t>
   </si>
   <si>
     <t>Blood in urine (haematuria) - symptoms, causes and treatment | healthdirect</t>
@@ -343,7 +343,7 @@
     <t>blurred-vision</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:04.097Z</t>
+    <t>2026-08-25T02:10:15.680Z</t>
   </si>
   <si>
     <t>Blurred vision - causes, symptoms and treatment | healthdirect</t>
@@ -361,7 +361,7 @@
     <t>brain-fog</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:12.741Z</t>
+    <t>2026-08-25T02:10:23.932Z</t>
   </si>
   <si>
     <t>Brain fog - symptoms, causes and treatment | healthdirect</t>
@@ -376,7 +376,7 @@
     <t>burping</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:21.320Z</t>
+    <t>2026-08-25T02:10:32.771Z</t>
   </si>
   <si>
     <t>Burping - belching | healthdirect</t>
@@ -394,7 +394,7 @@
     <t>calf-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:28.216Z</t>
+    <t>2026-08-25T02:10:41.127Z</t>
   </si>
   <si>
     <t>Calf pain - causes, treatment and prevention | healthdirect</t>
@@ -409,7 +409,7 @@
     <t>changes-to-your-appetite</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:34.372Z</t>
+    <t>2026-08-25T02:10:48.664Z</t>
   </si>
   <si>
     <t>Changes to your appetite | healthdirect</t>
@@ -427,7 +427,7 @@
     <t>chest-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:17:51.776Z</t>
+    <t>2026-08-25T02:10:57.677Z</t>
   </si>
   <si>
     <t>Chest pain | healthdirect</t>
@@ -442,7 +442,7 @@
     <t>chest-tightness-and-discomfort</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:40.670Z</t>
+    <t>2026-08-25T02:11:05.262Z</t>
   </si>
   <si>
     <t>Chest tightness and discomfort - left side pain, anxiety | healthdirect</t>
@@ -460,7 +460,7 @@
     <t>choking</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:48.245Z</t>
+    <t>2026-08-25T02:11:12.418Z</t>
   </si>
   <si>
     <t>Choking | healthdirect</t>
@@ -475,7 +475,7 @@
     <t>chronic-wounds</t>
   </si>
   <si>
-    <t>2026-08-24T04:41:55.457Z</t>
+    <t>2026-08-25T02:11:20.522Z</t>
   </si>
   <si>
     <t>Chronic wounds— causes, symptoms and treatment | healthdirect</t>
@@ -490,7 +490,7 @@
     <t>cognitive-impairment</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:03.444Z</t>
+    <t>2026-08-25T02:11:28.341Z</t>
   </si>
   <si>
     <t>Cognitive impairment - what it is and how to test for it | healthdirect</t>
@@ -505,7 +505,7 @@
     <t>confusion</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:11.705Z</t>
+    <t>2026-08-25T02:11:36.361Z</t>
   </si>
   <si>
     <t>Confusion - symptoms, causes and prevention | healthdirect</t>
@@ -520,7 +520,7 @@
     <t>constipation-in-children</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:28.016Z</t>
+    <t>2026-08-25T02:11:52.646Z</t>
   </si>
   <si>
     <t>Constipation in children | healthdirect</t>
@@ -535,7 +535,7 @@
     <t>constipation</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:20.219Z</t>
+    <t>2026-08-25T02:11:44.312Z</t>
   </si>
   <si>
     <t>Constipation - symptoms and treatment | healthdirect</t>
@@ -550,7 +550,7 @@
     <t>cough</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:36.301Z</t>
+    <t>2026-08-25T02:11:59.834Z</t>
   </si>
   <si>
     <t>Cough - types, treatments and remedies | healthdirect</t>
@@ -568,7 +568,7 @@
     <t>dealing-with-morning-sickness</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:43.464Z</t>
+    <t>2026-08-25T02:12:08.226Z</t>
   </si>
   <si>
     <t>Morning sickness | healthdirect</t>
@@ -586,7 +586,7 @@
     <t>delusions</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:49.895Z</t>
+    <t>2026-08-25T02:12:17.773Z</t>
   </si>
   <si>
     <t>Delusions | healthdirect</t>
@@ -601,7 +601,7 @@
     <t>diarrhoea-in-children</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:06.145Z</t>
+    <t>2026-08-25T02:12:33.653Z</t>
   </si>
   <si>
     <t>Diarrhoea in children - causes, care and treatments | healthdirect</t>
@@ -616,7 +616,7 @@
     <t>diarrhoea</t>
   </si>
   <si>
-    <t>2026-08-24T04:42:57.428Z</t>
+    <t>2026-08-25T02:12:24.540Z</t>
   </si>
   <si>
     <t>Diarrhoea - symptoms, causes, self care and treatments | healthdirect</t>
@@ -631,7 +631,7 @@
     <t>disorientation</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:13.039Z</t>
+    <t>2026-08-25T02:12:39.491Z</t>
   </si>
   <si>
     <t>Disorientation - symptoms, treatments and causes | healthdirect</t>
@@ -646,7 +646,7 @@
     <t>dizziness</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:20.970Z</t>
+    <t>2026-08-25T02:12:46.326Z</t>
   </si>
   <si>
     <t>Dizziness - symptoms, treatments and causes | healthdirect</t>
@@ -664,7 +664,7 @@
     <t>dry-eye-disease</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:28.101Z</t>
+    <t>2026-08-25T02:12:53.751Z</t>
   </si>
   <si>
     <t>Dry eyes | healthdirect</t>
@@ -679,7 +679,7 @@
     <t>earache</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:36.896Z</t>
+    <t>2026-08-25T02:13:00.180Z</t>
   </si>
   <si>
     <t>Earache – causes and treatments | healthdirect</t>
@@ -697,7 +697,7 @@
     <t>excessive-sweating-hyperhidrosis</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:43.795Z</t>
+    <t>2026-08-25T02:13:07.957Z</t>
   </si>
   <si>
     <t>Excessive sweating (hyperhidrosis) – causes and treatments | healthdirect</t>
@@ -712,7 +712,7 @@
     <t>excessive-worry</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:51.534Z</t>
+    <t>2026-08-25T02:13:15.061Z</t>
   </si>
   <si>
     <t>Excessive worry | healthdirect</t>
@@ -727,7 +727,7 @@
     <t>eye-discharge</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:59.736Z</t>
+    <t>2026-08-25T02:13:22.706Z</t>
   </si>
   <si>
     <t>Eye discharge - causes, diagnosis and treatment | healthdirect</t>
@@ -745,7 +745,7 @@
     <t>eye-strain</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:06.054Z</t>
+    <t>2026-08-25T02:13:31.377Z</t>
   </si>
   <si>
     <t>Eye strain | healthdirect</t>
@@ -760,7 +760,7 @@
     <t>facial-droop</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:13.885Z</t>
+    <t>2026-08-25T02:13:38.898Z</t>
   </si>
   <si>
     <t>Facial droop - causes and meaning | healthdirect</t>
@@ -778,7 +778,7 @@
     <t>faecal-incontinence</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:21.021Z</t>
+    <t>2026-08-25T02:13:47.270Z</t>
   </si>
   <si>
     <t>Faecal incontinence | healthdirect</t>
@@ -793,7 +793,7 @@
     <t>fainting</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:28.454Z</t>
+    <t>2026-08-25T02:13:54.868Z</t>
   </si>
   <si>
     <t>Fainting - treatments, symptoms, causes and prevention | healthdirect</t>
@@ -808,7 +808,7 @@
     <t>fatigue</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:34.582Z</t>
+    <t>2026-08-25T02:14:03.449Z</t>
   </si>
   <si>
     <t>Fatigue | healthdirect</t>
@@ -826,7 +826,7 @@
     <t>febrile-seizure</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:40.568Z</t>
+    <t>2026-08-25T02:14:10.721Z</t>
   </si>
   <si>
     <t>Febrile seizure - convulsion, fever | healthdirect</t>
@@ -841,7 +841,7 @@
     <t>feeling-restless</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:47.660Z</t>
+    <t>2026-08-25T02:14:17.226Z</t>
   </si>
   <si>
     <t>Feeling restless | healthdirect</t>
@@ -859,7 +859,7 @@
     <t>feeling-worthless</t>
   </si>
   <si>
-    <t>2026-08-24T04:44:59.140Z</t>
+    <t>2026-08-25T02:14:29.576Z</t>
   </si>
   <si>
     <t>Feeling worthless - self-help and other resources | healthdirect</t>
@@ -874,7 +874,7 @@
     <t>fever-and-high-temperature-in-children</t>
   </si>
   <si>
-    <t>2026-08-24T04:17:59.145Z</t>
+    <t>2026-08-25T02:14:44.817Z</t>
   </si>
   <si>
     <t>Fever and high temperature in children and babies - when to see a doctor | healthdirect</t>
@@ -889,7 +889,7 @@
     <t>fever</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:07.883Z</t>
+    <t>2026-08-25T02:14:38.242Z</t>
   </si>
   <si>
     <t>Fever - normal and high temperature range, when to see GP | healthdirect</t>
@@ -904,7 +904,7 @@
     <t>fluid-from-the-ear</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:13.723Z</t>
+    <t>2026-08-25T02:14:53.332Z</t>
   </si>
   <si>
     <t>Fluid from the ear - causes and treatments | healthdirect</t>
@@ -919,7 +919,7 @@
     <t>fluid-retention</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:23.198Z</t>
+    <t>2026-08-25T02:15:00.239Z</t>
   </si>
   <si>
     <t>Fluid retention | healthdirect</t>
@@ -934,7 +934,7 @@
     <t>frequent-urination</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:30.903Z</t>
+    <t>2026-08-25T02:15:08.849Z</t>
   </si>
   <si>
     <t>Frequent urination — nocturia | healthdirect</t>
@@ -952,7 +952,7 @@
     <t>groin-pain-or-swelling</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:38.673Z</t>
+    <t>2026-08-25T02:15:17.343Z</t>
   </si>
   <si>
     <t>Groin pain or swelling | healthdirect</t>
@@ -970,7 +970,7 @@
     <t>haemoptysis-coughing-up-blood</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:47.226Z</t>
+    <t>2026-08-25T02:15:24.837Z</t>
   </si>
   <si>
     <t>Haemoptysis (coughing up blood) | healthdirect</t>
@@ -985,7 +985,7 @@
     <t>halitosis</t>
   </si>
   <si>
-    <t>2026-08-24T04:45:54.339Z</t>
+    <t>2026-08-25T02:15:35.970Z</t>
   </si>
   <si>
     <t>Halitosis (bad breath) - related symptoms, treatments and prevention | healthdirect</t>
@@ -1000,7 +1000,7 @@
     <t>hallucination</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:01.789Z</t>
+    <t>2026-08-25T02:15:44.289Z</t>
   </si>
   <si>
     <t>Hallucination | healthdirect</t>
@@ -1015,7 +1015,7 @@
     <t>headaches</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:09.540Z</t>
+    <t>2026-08-25T02:15:51.192Z</t>
   </si>
   <si>
     <t>Headaches - types, causes, migraines, treatment and prevention | healthdirect</t>
@@ -1030,7 +1030,7 @@
     <t>heart-attack-symptoms-males-vs-females</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:17.741Z</t>
+    <t>2026-08-25T02:15:59.946Z</t>
   </si>
   <si>
     <t>Heart attack symptoms: males vs females | healthdirect</t>
@@ -1045,7 +1045,7 @@
     <t>heart-murmur</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:25.712Z</t>
+    <t>2026-08-25T02:16:07.306Z</t>
   </si>
   <si>
     <t>Heart murmur | healthdirect</t>
@@ -1060,7 +1060,7 @@
     <t>heart-palpitations</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:32.125Z</t>
+    <t>2026-08-25T02:16:14.360Z</t>
   </si>
   <si>
     <t>Heart palpitations - symptoms and causes | healthdirect</t>
@@ -1075,7 +1075,7 @@
     <t>heat-rash</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:41.069Z</t>
+    <t>2026-08-25T02:16:20.462Z</t>
   </si>
   <si>
     <t>Heat rash - treatments and causes | healthdirect</t>
@@ -1090,7 +1090,7 @@
     <t>heavy-periods</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:47.856Z</t>
+    <t>2026-08-25T02:16:29.030Z</t>
   </si>
   <si>
     <t>Heavy periods (menorrhagia) | healthdirect</t>
@@ -1105,7 +1105,7 @@
     <t>heel-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:46:54.525Z</t>
+    <t>2026-08-25T02:16:37.807Z</t>
   </si>
   <si>
     <t>Heel pain | healthdirect</t>
@@ -1120,7 +1120,7 @@
     <t>hiccups</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:02.352Z</t>
+    <t>2026-08-25T02:16:44.441Z</t>
   </si>
   <si>
     <t>Hiccups - causes and how to get rid of hiccups | healthdirect</t>
@@ -1135,7 +1135,7 @@
     <t>hip-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:10.169Z</t>
+    <t>2026-08-25T02:16:52.946Z</t>
   </si>
   <si>
     <t>Hip pain | healthdirect</t>
@@ -1150,7 +1150,7 @@
     <t>hot-flushes-due-to-menopause</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:18.505Z</t>
+    <t>2026-08-25T02:17:01.652Z</t>
   </si>
   <si>
     <t>Hot flushes due to menopause | healthdirect</t>
@@ -1168,7 +1168,7 @@
     <t>indigestion</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:26.807Z</t>
+    <t>2026-08-25T02:17:09.225Z</t>
   </si>
   <si>
     <t>Indigestion (dyspepsia) - treatment | healthdirect</t>
@@ -1183,7 +1183,7 @@
     <t>irregular-periods</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:34.265Z</t>
+    <t>2026-08-25T02:17:16.435Z</t>
   </si>
   <si>
     <t>Irregular periods | healthdirect</t>
@@ -1201,7 +1201,7 @@
     <t>irritability-and-feeling-on-edge</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:42.146Z</t>
+    <t>2026-08-25T02:17:24.812Z</t>
   </si>
   <si>
     <t>Irritability and feeling on edge | healthdirect</t>
@@ -1216,7 +1216,7 @@
     <t>itchy-anus</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:49.805Z</t>
+    <t>2026-08-25T02:17:32.953Z</t>
   </si>
   <si>
     <t>Itchy anus (pruritus ani) | healthdirect</t>
@@ -1231,7 +1231,7 @@
     <t>itchy-scalp</t>
   </si>
   <si>
-    <t>2026-08-24T04:47:56.877Z</t>
+    <t>2026-08-25T02:17:41.645Z</t>
   </si>
   <si>
     <t>Itchy scalp - causes, treatment and prevention | healthdirect</t>
@@ -1246,7 +1246,7 @@
     <t>itchy-skin</t>
   </si>
   <si>
-    <t>2026-08-24T04:48:04.552Z</t>
+    <t>2026-08-25T02:17:49.671Z</t>
   </si>
   <si>
     <t>Itchy skin - treatments, causes and prevention | healthdirect</t>
@@ -1264,7 +1264,7 @@
     <t>jaundice</t>
   </si>
   <si>
-    <t>2026-08-24T04:48:14.526Z</t>
+    <t>2026-08-25T02:17:59.126Z</t>
   </si>
   <si>
     <t>Jaundice in adults | healthdirect</t>
@@ -1279,7 +1279,7 @@
     <t>joint-pain-and-swelling</t>
   </si>
   <si>
-    <t>2026-08-24T04:48:20.698Z</t>
+    <t>2026-08-25T02:18:06.342Z</t>
   </si>
   <si>
     <t>Joint pain and swelling - symptoms, causes and treatments | healthdirect</t>
@@ -1294,7 +1294,7 @@
     <t>kidney-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:48:27.379Z</t>
+    <t>2026-08-25T02:18:13.179Z</t>
   </si>
   <si>
     <t>Kidney pain | healthdirect</t>
@@ -1309,7 +1309,7 @@
     <t>knee-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:48:33.792Z</t>
+    <t>2026-08-25T02:18:20.461Z</t>
   </si>
   <si>
     <t>Knee pain | healthdirect</t>
@@ -1324,7 +1324,7 @@
     <t>leg-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:04.407Z</t>
+    <t>2026-08-25T02:18:27.794Z</t>
   </si>
   <si>
     <t>Leg pain - related symptoms, causes and treatments | healthdirect</t>
@@ -1339,7 +1339,7 @@
     <t>lightheadedness</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:13.503Z</t>
+    <t>2026-08-25T02:18:35.152Z</t>
   </si>
   <si>
     <t>Lightheadedness - causes, treatment and prevention | healthdirect</t>
@@ -1354,7 +1354,7 @@
     <t>limb-numbness</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:20.981Z</t>
+    <t>2026-08-25T02:18:42.467Z</t>
   </si>
   <si>
     <t>Limb numbness - causes, treatment and prevention | healthdirect</t>
@@ -1369,7 +1369,7 @@
     <t>losing-interest</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:27.497Z</t>
+    <t>2026-08-25T02:18:49.516Z</t>
   </si>
   <si>
     <t>Losing interest | healthdirect</t>
@@ -1384,7 +1384,7 @@
     <t>low-back-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:34.144Z</t>
+    <t>2026-08-25T02:18:56.846Z</t>
   </si>
   <si>
     <t>Low back pain - causes, symptoms, diagnosis | healthdirect</t>
@@ -1399,7 +1399,7 @@
     <t>lump-under-armpit</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:44.501Z</t>
+    <t>2026-08-25T02:19:04.127Z</t>
   </si>
   <si>
     <t>Lump under armpit - enlarged lymph nodes under arms | healthdirect</t>
@@ -1414,7 +1414,7 @@
     <t>managing-mood-swings</t>
   </si>
   <si>
-    <t>2026-08-24T04:49:51.872Z</t>
+    <t>2026-08-25T02:19:11.378Z</t>
   </si>
   <si>
     <t>Mood swings and low mood — what to do | healthdirect</t>
@@ -1429,7 +1429,7 @@
     <t>motion-sickness</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:01.093Z</t>
+    <t>2026-08-25T02:19:17.870Z</t>
   </si>
   <si>
     <t>Motion sickness - travel, sea, car, medication | healthdirect</t>
@@ -1444,7 +1444,7 @@
     <t>muscle-aches-and-pains</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:09.061Z</t>
+    <t>2026-08-25T02:19:25.401Z</t>
   </si>
   <si>
     <t>Muscle aches and pains | healthdirect</t>
@@ -1459,7 +1459,7 @@
     <t>nausea</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:15.341Z</t>
+    <t>2026-08-25T02:19:32.081Z</t>
   </si>
   <si>
     <t>Nausea | healthdirect</t>
@@ -1474,7 +1474,7 @@
     <t>nerve-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:23.036Z</t>
+    <t>2026-08-25T02:19:38.794Z</t>
   </si>
   <si>
     <t>Nerve pain (neuralgia) - causes, diagnosis and treatments | healthdirect</t>
@@ -1489,7 +1489,7 @@
     <t>night-sweats</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:30.391Z</t>
+    <t>2026-08-25T02:19:45.957Z</t>
   </si>
   <si>
     <t>Night sweats - symptoms, treatments and causes | healthdirect</t>
@@ -1504,7 +1504,7 @@
     <t>nosebleed</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:39.694Z</t>
+    <t>2026-08-25T02:19:54.397Z</t>
   </si>
   <si>
     <t>Nosebleeds - epistaxis, treatments and prevention | healthdirect</t>
@@ -1519,7 +1519,7 @@
     <t>painful-sex-for-women</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:46.312Z</t>
+    <t>2026-08-25T02:20:01.323Z</t>
   </si>
   <si>
     <t>Painful sex for women | healthdirect</t>
@@ -1534,7 +1534,7 @@
     <t>penis-irritation</t>
   </si>
   <si>
-    <t>2026-08-24T04:50:55.335Z</t>
+    <t>2026-08-25T02:20:09.031Z</t>
   </si>
   <si>
     <t>Penis irritation | healthdirect</t>
@@ -1549,7 +1549,7 @@
     <t>penis-swelling-and-injury</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:03.074Z</t>
+    <t>2026-08-25T02:20:15.441Z</t>
   </si>
   <si>
     <t>Penis injury, swelling or pain | healthdirect</t>
@@ -1564,7 +1564,7 @@
     <t>persistent-pelvic-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:11.442Z</t>
+    <t>2026-08-25T02:20:23.223Z</t>
   </si>
   <si>
     <t>Persistent pelvic pain | healthdirect</t>
@@ -1579,7 +1579,7 @@
     <t>rashes</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:19.573Z</t>
+    <t>2026-08-25T02:20:31.569Z</t>
   </si>
   <si>
     <t>Rashes | healthdirect</t>
@@ -1594,7 +1594,7 @@
     <t>rectal-bleeding</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:27.357Z</t>
+    <t>2026-08-25T02:20:37.874Z</t>
   </si>
   <si>
     <t>Rectal bleeding - treatments, causes and related symptoms | healthdirect</t>
@@ -1609,7 +1609,7 @@
     <t>runny-nose</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:33.925Z</t>
+    <t>2026-08-25T02:20:45.822Z</t>
   </si>
   <si>
     <t>Runny nose - treatment | healthdirect</t>
@@ -1624,7 +1624,7 @@
     <t>separation-anxiety</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:41.666Z</t>
+    <t>2026-08-25T02:20:53.439Z</t>
   </si>
   <si>
     <t>Separation anxiety | healthdirect</t>
@@ -1642,7 +1642,7 @@
     <t>shortness-of-breath</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:49.225Z</t>
+    <t>2026-08-25T02:21:02.168Z</t>
   </si>
   <si>
     <t>Shortness of breath (dyspnoea) - causes, symptoms and treatments | healthdirect</t>
@@ -1657,7 +1657,7 @@
     <t>shoulder-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:51:57.437Z</t>
+    <t>2026-08-25T02:21:09.538Z</t>
   </si>
   <si>
     <t>Shoulder pain | healthdirect</t>
@@ -1675,7 +1675,7 @@
     <t>signs-of-mental-health-issues</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:06.279Z</t>
+    <t>2026-08-25T02:21:17.683Z</t>
   </si>
   <si>
     <t>Signs of mental health issues | healthdirect</t>
@@ -1690,7 +1690,7 @@
     <t>sneezing</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:15.242Z</t>
+    <t>2026-08-25T02:21:26.018Z</t>
   </si>
   <si>
     <t>Sneezing — runny nose | healthdirect</t>
@@ -1705,7 +1705,7 @@
     <t>sore-throat</t>
   </si>
   <si>
-    <t>2026-08-24T04:18:15.242Z</t>
+    <t>2026-08-25T02:21:34.989Z</t>
   </si>
   <si>
     <t>Sore throat (pharyngitis) - symptoms, treatments and causes | healthdirect</t>
@@ -1720,7 +1720,7 @@
     <t>summer-skin-rashes</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:22.096Z</t>
+    <t>2026-08-25T02:21:43.270Z</t>
   </si>
   <si>
     <t>Summer skin rashes - heat rash, hives and treatment | healthdirect</t>
@@ -1735,7 +1735,7 @@
     <t>swollen-gums</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:29.824Z</t>
+    <t>2026-08-25T02:21:51.359Z</t>
   </si>
   <si>
     <t>Swollen gums — red, inflamed | healthdirect</t>
@@ -1750,7 +1750,7 @@
     <t>swollen-or-painful-testicle</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:36.298Z</t>
+    <t>2026-08-25T02:21:59.545Z</t>
   </si>
   <si>
     <t>Swollen or painful testicle | healthdirect</t>
@@ -1768,7 +1768,7 @@
     <t>symptoms-of-serious-illness-in-babies-and-children</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:45.545Z</t>
+    <t>2026-08-25T02:22:08.471Z</t>
   </si>
   <si>
     <t>Symptoms of serious illness in babies and children | healthdirect</t>
@@ -1783,7 +1783,7 @@
     <t>tachycardia</t>
   </si>
   <si>
-    <t>2026-08-24T04:52:54.107Z</t>
+    <t>2026-08-25T02:22:16.761Z</t>
   </si>
   <si>
     <t>Tachycardia - symptoms and treatment | healthdirect</t>
@@ -1798,7 +1798,7 @@
     <t>tinnitus</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:02.283Z</t>
+    <t>2026-08-25T02:22:25.569Z</t>
   </si>
   <si>
     <t>Tinnitus (ringing in the ears) - causes, symptoms, treatments | healthdirect</t>
@@ -1813,7 +1813,7 @@
     <t>toothache-and-gum-swelling</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:10.470Z</t>
+    <t>2026-08-25T02:22:34.688Z</t>
   </si>
   <si>
     <t>Toothache and gum swelling – causes and treatment | healthdirect</t>
@@ -1828,7 +1828,7 @@
     <t>unpleasant-thoughts</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:16.165Z</t>
+    <t>2026-08-25T02:22:40.823Z</t>
   </si>
   <si>
     <t>Unpleasant thoughts | healthdirect</t>
@@ -1843,7 +1843,7 @@
     <t>urinary-retention</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:22.920Z</t>
+    <t>2026-08-25T02:22:48.211Z</t>
   </si>
   <si>
     <t>Urinary retention | healthdirect</t>
@@ -1858,7 +1858,7 @@
     <t>vaginal-discharge</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:29.552Z</t>
+    <t>2026-08-25T02:22:57.099Z</t>
   </si>
   <si>
     <t>Vaginal discharge | healthdirect</t>
@@ -1873,7 +1873,7 @@
     <t>vaginal-dryness</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:37.291Z</t>
+    <t>2026-08-25T02:23:04.501Z</t>
   </si>
   <si>
     <t>Vaginal dryness – treatment and symptoms | healthdirect</t>
@@ -1888,7 +1888,7 @@
     <t>vaginal-irritation-and-infection</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:44.896Z</t>
+    <t>2026-08-25T02:23:12.746Z</t>
   </si>
   <si>
     <t>Vaginal and irritation and infection | healthdirect</t>
@@ -1903,7 +1903,7 @@
     <t>vertigo</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:52.627Z</t>
+    <t>2026-08-25T02:23:21.518Z</t>
   </si>
   <si>
     <t>Vertigo - symptoms, causes and treatments | healthdirect</t>
@@ -1921,7 +1921,7 @@
     <t>vomiting-in-children</t>
   </si>
   <si>
-    <t>2026-08-24T04:54:07.585Z</t>
+    <t>2026-08-25T02:23:37.104Z</t>
   </si>
   <si>
     <t>Vomiting in children - treatments, self-care and causes | healthdirect</t>
@@ -1936,7 +1936,7 @@
     <t>vomiting</t>
   </si>
   <si>
-    <t>2026-08-24T04:53:59.709Z</t>
+    <t>2026-08-25T02:23:29.200Z</t>
   </si>
   <si>
     <t>Vomiting - treatments, self-care and causes | healthdirect</t>
@@ -1954,7 +1954,7 @@
     <t>warning-signs-during-pregnancy</t>
   </si>
   <si>
-    <t>2026-08-24T04:54:15.172Z</t>
+    <t>2026-08-25T02:23:45.785Z</t>
   </si>
   <si>
     <t>Warning signs during pregnancy | healthdirect</t>
@@ -1972,7 +1972,7 @@
     <t>wheezing</t>
   </si>
   <si>
-    <t>2026-08-24T04:54:22.548Z</t>
+    <t>2026-08-25T02:23:52.863Z</t>
   </si>
   <si>
     <t>Wheezing | healthdirect</t>
@@ -1990,7 +1990,7 @@
     <t>wrist-pain</t>
   </si>
   <si>
-    <t>2026-08-24T04:54:29.022Z</t>
+    <t>2026-08-25T02:24:00.528Z</t>
   </si>
   <si>
     <t>Wrist pain - causes, diagnosis and treatment | healthdirect</t>
